--- a/data/db/documents.xlsx
+++ b/data/db/documents.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F947"/>
+  <dimension ref="A1:F1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29805,6 +29805,2342 @@
         </is>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" s="1" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="B948" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-08-01</t>
+        </is>
+      </c>
+      <c r="C948" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Rougher 1st Concentrate Hopper 1 3310-08-01</t>
+        </is>
+      </c>
+      <c r="D948" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E948" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F948" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="1" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="B949" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-08-01</t>
+        </is>
+      </c>
+      <c r="C949" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Rougher 1st Concentrate Hopper 1</t>
+        </is>
+      </c>
+      <c r="D949" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E949" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F949" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="1" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="B950" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-08-01</t>
+        </is>
+      </c>
+      <c r="C950" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3310-08-01 Rougher 1st Concentrate Hopper 1</t>
+        </is>
+      </c>
+      <c r="D950" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E950" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F950" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="1" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="B951" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C951" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Rougher 2nd Concentrate Hopper 1 3310-09-01</t>
+        </is>
+      </c>
+      <c r="D951" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E951" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F951" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="1" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="B952" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C952" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Rougher 2nd Concentrate Hopper 1</t>
+        </is>
+      </c>
+      <c r="D952" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E952" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F952" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="1" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="B953" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-09-01</t>
+        </is>
+      </c>
+      <c r="C953" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3310-09-01 Rougher 2nd Concentrate Hopper 1</t>
+        </is>
+      </c>
+      <c r="D953" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E953" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F953" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="1" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="B954" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C954" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Rougher 1st Concentrate Hopper 2 Pump 2 3310-17-03</t>
+        </is>
+      </c>
+      <c r="D954" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E954" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F954" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="1" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="B955" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C955" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Rougher 1st Concentrate Hopper 2 Pump 2</t>
+        </is>
+      </c>
+      <c r="D955" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E955" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F955" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="1" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="B956" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C956" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3310-17-03 Rougher 1st Concentrate Hopper 2 Pump 2 &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D956" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E956" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F956" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="1" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="B957" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-17-03</t>
+        </is>
+      </c>
+      <c r="C957" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3310-17-03 Rougher 1st Concentrate Hopper 2 Pump 2 &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D957" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E957" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F957" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="1" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="B958" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C958" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of CCD Thickener Area Sump Pump 1 3510-01-01</t>
+        </is>
+      </c>
+      <c r="D958" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E958" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F958" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="1" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="B959" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C959" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of CCD Thickener Area Sump Pump 1</t>
+        </is>
+      </c>
+      <c r="D959" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E959" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F959" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="1" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="B960" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C960" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3510-01-01 CCD Thickener Area Sump Pump 1</t>
+        </is>
+      </c>
+      <c r="D960" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E960" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F960" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="1" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="B961" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3510-01-01</t>
+        </is>
+      </c>
+      <c r="C961" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3510-01-01  CCD Thickener Area Sump Pump 1</t>
+        </is>
+      </c>
+      <c r="D961" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E961" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F961" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="1" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="B962" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C962" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of CCD Thickener 6  Feed Box 3510-04-01</t>
+        </is>
+      </c>
+      <c r="D962" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E962" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F962" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="1" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="B963" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C963" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of CCD Thickener 6 Feed Box</t>
+        </is>
+      </c>
+      <c r="D963" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E963" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F963" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="1" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="B964" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3510-04-01</t>
+        </is>
+      </c>
+      <c r="C964" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3510-04-01 CCD Thickener 6 Feed Box</t>
+        </is>
+      </c>
+      <c r="D964" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E964" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F964" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="1" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="B965" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C965" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Concentrate Storage  Distribution Box 3530-01-04</t>
+        </is>
+      </c>
+      <c r="D965" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E965" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F965" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="1" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="B966" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C966" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Concentrate Storage Distribution Box</t>
+        </is>
+      </c>
+      <c r="D966" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E966" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F966" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="1" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="B967" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3530-01-04</t>
+        </is>
+      </c>
+      <c r="C967" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3530-01-04 Concentrate Storage Distribution Box</t>
+        </is>
+      </c>
+      <c r="D967" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E967" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F967" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="1" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="B968" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C968" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3410-06-02 3411-PU-173 Coarse Cleaner Tails Pump 1</t>
+        </is>
+      </c>
+      <c r="D968" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E968" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F968" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="1" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="B969" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C969" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Coarse Cleaner Tails Pump 1 VSD</t>
+        </is>
+      </c>
+      <c r="D969" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E969" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F969" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="1" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="B970" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C970" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3410-06-04 Rougher Flotation Area Sump Pumps 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="D970" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E970" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F970" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="1" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="B971" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-06-02</t>
+        </is>
+      </c>
+      <c r="C971" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3410-06-02 Coarse Cleaner Tails Pump 1 VSD</t>
+        </is>
+      </c>
+      <c r="D971" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E971" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F971" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="1" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="B972" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C972" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3420-15-02 3422-FC-072 3rd Oxide Cleaner Cell 2</t>
+        </is>
+      </c>
+      <c r="D972" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E972" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F972" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="B973" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C973" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of 3rd Oxide Cleaner Cell 2</t>
+        </is>
+      </c>
+      <c r="D973" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E973" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F973" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="B974" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3420-15-02</t>
+        </is>
+      </c>
+      <c r="C974" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3420-15-02 1st Sulfide Cleaner Standby Feed Pump VSD</t>
+        </is>
+      </c>
+      <c r="D974" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E974" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F974" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="B975" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C975" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 4 Cyclone Feed Hopper 3122-CH-406 HO-404</t>
+        </is>
+      </c>
+      <c r="D975" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E975" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F975" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="B976" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C976" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Ball Mill 6 Cooling Water</t>
+        </is>
+      </c>
+      <c r="D976" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E976" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F976" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="B977" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3120-02-01</t>
+        </is>
+      </c>
+      <c r="C977" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3120-02-01 Line 4 Cyclone Feed Hopper</t>
+        </is>
+      </c>
+      <c r="D977" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E977" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F977" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="B978" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C978" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends 3112-ME-303 3112-ME-304 3113-PU-351</t>
+        </is>
+      </c>
+      <c r="D978" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E978" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F978" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="B979" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CY-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C979" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends</t>
+        </is>
+      </c>
+      <c r="D979" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E979" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F979" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="B980" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C980" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3110-02-03 Line 3 Cyclone Cluster 5 Feed Pump &amp; VSD &amp; Horizontal &amp; Vertical Bends</t>
+        </is>
+      </c>
+      <c r="D980" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E980" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F980" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="B981" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3110-02-03</t>
+        </is>
+      </c>
+      <c r="C981" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3110-02-03 Line 3 Cyclone Cluster 5 Feed Pump</t>
+        </is>
+      </c>
+      <c r="D981" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E981" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F981" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="B982" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C982" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen 2320-01-02</t>
+        </is>
+      </c>
+      <c r="D982" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E982" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F982" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="B983" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-SP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C983" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+      <c r="D983" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E983" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F983" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="B984" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C984" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2320-01-02 Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+      <c r="D984" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E984" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F984" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="B985" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-01-02</t>
+        </is>
+      </c>
+      <c r="C985" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2320-01-02 Line 4 SAG Mill Feed Conveyor Area Sump Pump &amp; Screen</t>
+        </is>
+      </c>
+      <c r="D985" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E985" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F985" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="B986" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="C986" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 4 SAG Mill New &amp; Total Feed Conveyor Weightometers 2320-01-04</t>
+        </is>
+      </c>
+      <c r="D986" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E986" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F986" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="B987" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2320-01-04</t>
+        </is>
+      </c>
+      <c r="C987" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2320-01-04 Line 4 SAG Mill New &amp; Total Feed Conveyor Weightometers</t>
+        </is>
+      </c>
+      <c r="D987" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E987" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F987" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="B988" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="C988" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 3 SAG Mill Conveyor Motor 2320-02-05</t>
+        </is>
+      </c>
+      <c r="D988" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E988" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F988" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="B989" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2320-02-05</t>
+        </is>
+      </c>
+      <c r="C989" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2320-02-05 Line 3 SAG Mill Conveyor Motor</t>
+        </is>
+      </c>
+      <c r="D989" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E989" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F989" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="B990" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-05-02</t>
+        </is>
+      </c>
+      <c r="C990" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-05-02 2311-FE-401 Image Analyzing System</t>
+        </is>
+      </c>
+      <c r="D990" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E990" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F990" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="B991" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-06-02</t>
+        </is>
+      </c>
+      <c r="C991" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-06-02 2311-FE-402 Image Analyzing System</t>
+        </is>
+      </c>
+      <c r="D991" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E991" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F991" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="B992" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2310-07-02</t>
+        </is>
+      </c>
+      <c r="C992" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2310-07-02 2311-FE-403 Image Analyzing System</t>
+        </is>
+      </c>
+      <c r="D992" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E992" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F992" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="B993" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C993" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of OLC 2 Transfer Area Fire Water Tank 2120-01-02</t>
+        </is>
+      </c>
+      <c r="D993" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E993" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F993" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="B994" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C994" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of OLC 2 Transfer Area Fire Water Tank</t>
+        </is>
+      </c>
+      <c r="D994" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E994" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F994" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="B995" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2120-01-02</t>
+        </is>
+      </c>
+      <c r="C995" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2120-01-02 OLC 2 Transfer Area Fire Water Tank</t>
+        </is>
+      </c>
+      <c r="D995" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E995" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F995" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="B996" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C996" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Fire Water Pumps Package Vendor Package 2120-01-01</t>
+        </is>
+      </c>
+      <c r="D996" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E996" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F996" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="B997" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FW-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C997" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Fire Water Pumps Package Vendor Package</t>
+        </is>
+      </c>
+      <c r="D997" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E997" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F997" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="B998" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2120-01-01</t>
+        </is>
+      </c>
+      <c r="C998" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2120-01-01 Fire Water Pumps</t>
+        </is>
+      </c>
+      <c r="D998" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E998" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F998" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="1" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="B999" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="C999" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3&amp;4 Discharge Conveyor Head Pulley Replacement Hoist 2110-90-09</t>
+        </is>
+      </c>
+      <c r="D999" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E999" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F999" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="B1000" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2110-90-09</t>
+        </is>
+      </c>
+      <c r="C1000" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2110-90-09 Primary Crusher 3 &amp; 4 Discharge Conveyor Head Pulley Replacement Hoist</t>
+        </is>
+      </c>
+      <c r="D1000" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1000" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1000" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="B1001" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1001" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2100-01-01/02/03 Primary Crusher 3 Discharge Chute Air Cannon 1/2/3</t>
+        </is>
+      </c>
+      <c r="D1001" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1001" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1001" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="B1002" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-02</t>
+        </is>
+      </c>
+      <c r="C1002" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3 Discharge Chute Air Cannon 2 2100-01-02</t>
+        </is>
+      </c>
+      <c r="D1002" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1002" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1002" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="B1003" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1003" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of CCD 6 Flocculant Mixer 3580-02-04</t>
+        </is>
+      </c>
+      <c r="D1003" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1003" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1003" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="B1004" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FL-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1004" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of CCD 6 Flocculant Mixer</t>
+        </is>
+      </c>
+      <c r="D1004" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1004" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1004" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="B1005" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-02-04</t>
+        </is>
+      </c>
+      <c r="C1005" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-02-04 CCD 6 Flocculant Mixer</t>
+        </is>
+      </c>
+      <c r="D1005" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1005" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1005" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="B1006" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1006" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Transfer Pumps 1 3580-07-01</t>
+        </is>
+      </c>
+      <c r="D1006" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1006" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1006" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="B1007" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1007" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Transfer Pump 1</t>
+        </is>
+      </c>
+      <c r="D1007" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1007" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1007" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="1" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="B1008" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1008" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-07-01 Lime Transfer Pump 1</t>
+        </is>
+      </c>
+      <c r="D1008" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1008" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1008" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="1" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="B1009" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-07-01</t>
+        </is>
+      </c>
+      <c r="C1009" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-07-01 Lime Transfer Pump 1</t>
+        </is>
+      </c>
+      <c r="D1009" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1009" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1009" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="1" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="B1010" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1010" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3580-08-04 Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+      <c r="D1010" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1010" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1010" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="1" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="B1011" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-GWP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1011" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+      <c r="D1011" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1011" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1011" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="1" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="B1012" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1012" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-08-04 Grinding Lime Ring main Pump 1</t>
+        </is>
+      </c>
+      <c r="D1012" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1012" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1012" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="1" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B1013" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3580-08-04</t>
+        </is>
+      </c>
+      <c r="C1013" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-08-04 Grinding Lime Ringmain Pump 1</t>
+        </is>
+      </c>
+      <c r="D1013" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1013" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1013" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="1" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B1014" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1014" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3 Discharge Chute Air Cannon 1 2100-01-01</t>
+        </is>
+      </c>
+      <c r="D1014" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1014" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1014" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="1" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B1015" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-AP-2100-01-01</t>
+        </is>
+      </c>
+      <c r="C1015" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Primary Crusher 3 Discharge Chute Air Cannon 1</t>
+        </is>
+      </c>
+      <c r="D1015" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1015" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1015" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="1" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B1016" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2191-50-09</t>
+        </is>
+      </c>
+      <c r="C1016" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2191-50-09 2111-WO-001 Welding Outlet</t>
+        </is>
+      </c>
+      <c r="D1016" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1016" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1016" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="1" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B1017" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2114-90-01</t>
+        </is>
+      </c>
+      <c r="C1017" s="1" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 2114-90-01 Camera-Network</t>
+        </is>
+      </c>
+      <c r="D1017" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1017" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1017" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="1" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="B1018" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3191-90-01</t>
+        </is>
+      </c>
+      <c r="C1018" s="1" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3191-90-01 Camera-Network</t>
+        </is>
+      </c>
+      <c r="D1018" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1018" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1018" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="1" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="B1019" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3193-90-01</t>
+        </is>
+      </c>
+      <c r="C1019" s="1" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3193-90-01 Camera-Network</t>
+        </is>
+      </c>
+      <c r="D1019" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1019" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1019" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="1" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B1020" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3591-90-01</t>
+        </is>
+      </c>
+      <c r="C1020" s="1" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 3591-90-01 Camera-Network</t>
+        </is>
+      </c>
+      <c r="D1020" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1020" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1020" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/db/documents.xlsx
+++ b/data/db/documents.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1020"/>
+  <dimension ref="A1:F1047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32141,6 +32141,870 @@
         </is>
       </c>
     </row>
+    <row r="1021">
+      <c r="A1021" s="1" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="B1021" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1021" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3310-21-02 Line 8 Rougher Cell 1 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1021" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1021" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1021" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="1" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="B1022" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1022" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Line 8 Rougher Cell 1</t>
+        </is>
+      </c>
+      <c r="D1022" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1022" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1022" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="1" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="B1023" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1023" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3310-21-02 Line 8 Rougher Cell 1 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1023" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1023" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1023" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="1" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="B1024" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3310-21-02</t>
+        </is>
+      </c>
+      <c r="C1024" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3310-21-02 Line 8 Rougher Cell 1 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1024" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1024" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1024" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="B1025" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3210-01-01</t>
+        </is>
+      </c>
+      <c r="C1025" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3210-01-01 3211-CH-051 3211-CH-052 3211-CH-053 3211-CH-054 3211-CH-055 3211-CH-056 3211-BN-009 Pebble Crusher Transfer Bin</t>
+        </is>
+      </c>
+      <c r="D1025" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1025" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1025" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="1" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="B1026" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3210-01-01</t>
+        </is>
+      </c>
+      <c r="C1026" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3210-01-01 Pebble Crusher Transfer Bin</t>
+        </is>
+      </c>
+      <c r="D1026" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1026" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1026" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="1" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="B1027" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1027" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3410-02-02 3411-PU-063 Coarse Cleaner Flotation Column 1 Standby Feed VSD Pump</t>
+        </is>
+      </c>
+      <c r="D1027" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1027" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1027" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="B1028" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1028" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Coarse Cleaner Flotation Column Standby Feed Pump &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1028" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1028" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1028" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="B1029" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1029" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3410-02-02 Coarse Cleaner Flotation Column Standby Feed Pump &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1029" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1029" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1029" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="1" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="B1030" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-02-02</t>
+        </is>
+      </c>
+      <c r="C1030" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3410-02-02 Coarse Cleaner Flotation Column Standby Feed Pump &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1030" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1030" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1030" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="1" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="B1031" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1031" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3410-11-03 3412-FC-033 3412-FC-033-M01 1st Sulfide Cleaner 1 Cell 3</t>
+        </is>
+      </c>
+      <c r="D1031" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1031" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1031" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="1" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="B1032" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FT-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1032" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of 1st Sulfide Cleaner 1 Cell 3 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1032" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1032" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1032" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="1" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="B1033" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1033" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3410-11-03 1st Sulfide Cleaner 1 Cell 3 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1033" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1033" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1033" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="1" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="B1034" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-11-03</t>
+        </is>
+      </c>
+      <c r="C1034" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3410-11-03 1st Sulfide Cleaner 1 Cell 3 &amp; Agitator</t>
+        </is>
+      </c>
+      <c r="D1034" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1034" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1034" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="1" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="B1035" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1035" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3410-16-02 3412-PU-089 1st Sulfide Cleaner Concentrate Transfer Pump 1</t>
+        </is>
+      </c>
+      <c r="D1035" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1035" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1035" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="1" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="B1036" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-FC-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1036" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of 1st Sulfide Cleaner Concentrate Transfer Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1036" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1036" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1036" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="1" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="B1037" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1037" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3410-16-02 Sulfide Cleaner 1st Concentrate Transfer Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1037" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1037" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1037" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="B1038" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-3410-16-02</t>
+        </is>
+      </c>
+      <c r="C1038" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3410-16-02 1st Sulfide Cleaner Concentrate Transfer Pump 1 &amp; VSD</t>
+        </is>
+      </c>
+      <c r="D1038" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1038" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1038" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="B1039" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-3000-02-01</t>
+        </is>
+      </c>
+      <c r="C1039" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Line 6 Rougher Tails Sampler 3000-02-01</t>
+        </is>
+      </c>
+      <c r="D1039" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1039" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1039" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="B1040" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-PRW-3000-02-01</t>
+        </is>
+      </c>
+      <c r="C1040" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Line 6 Rougher Tails Sampler</t>
+        </is>
+      </c>
+      <c r="D1040" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1040" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1040" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="B1041" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-4110-03-01</t>
+        </is>
+      </c>
+      <c r="C1041" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 4110-03-01 Filtrate Thickener Feed Box</t>
+        </is>
+      </c>
+      <c r="D1041" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1041" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1041" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="1" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="B1042" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-50-HOP-CC-4110-03-01</t>
+        </is>
+      </c>
+      <c r="C1042" s="1" t="inlineStr">
+        <is>
+          <t>Piping HOP of Filtrate Thickener Feed Box</t>
+        </is>
+      </c>
+      <c r="D1042" s="1" t="inlineStr">
+        <is>
+          <t>Piping</t>
+        </is>
+      </c>
+      <c r="E1042" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1042" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="1" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="B1043" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1043" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Primary Crusher 3 2110-01-01</t>
+        </is>
+      </c>
+      <c r="D1043" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1043" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1043" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="1" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="B1044" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1044" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 2110-01-01 Primary Crusher 3</t>
+        </is>
+      </c>
+      <c r="D1044" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1044" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1044" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="B1045" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-70-HOP-2110-01-01</t>
+        </is>
+      </c>
+      <c r="C1045" s="1" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 2110-01-01 Primary Crusher 3</t>
+        </is>
+      </c>
+      <c r="D1045" s="1" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E1045" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1045" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="B1046" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-59-HOP-4130-90-01</t>
+        </is>
+      </c>
+      <c r="C1046" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Concentrate Pump Station Maintenance Hoist 4130-90-01</t>
+        </is>
+      </c>
+      <c r="D1046" s="1" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="E1046" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1046" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="B1047" s="1" t="inlineStr">
+        <is>
+          <t>PR2ME-PIL-QTY-65-HOP-4130-90-01</t>
+        </is>
+      </c>
+      <c r="C1047" s="1" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 4130-90-01 Concentrate Pump Station Maintenance Hoist</t>
+        </is>
+      </c>
+      <c r="D1047" s="1" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="E1047" s="1" t="inlineStr">
+        <is>
+          <t>UPLOADED_FILE</t>
+        </is>
+      </c>
+      <c r="F1047" s="1" t="inlineStr">
+        <is>
+          <t>HOP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/db/documents.xlsx
+++ b/data/db/documents.xlsx
@@ -33040,7 +33040,7 @@
       </c>
       <c r="E1048" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1048" s="2" t="inlineStr">
@@ -33072,7 +33072,7 @@
       </c>
       <c r="E1049" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1049" s="2" t="inlineStr">
@@ -33104,7 +33104,7 @@
       </c>
       <c r="E1050" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1050" s="2" t="inlineStr">
@@ -33136,7 +33136,7 @@
       </c>
       <c r="E1051" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1051" s="2" t="inlineStr">
@@ -33168,7 +33168,7 @@
       </c>
       <c r="E1052" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1052" s="2" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="E1053" s="2" t="inlineStr">
         <is>
-          <t>DOWNLOADED</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1053" s="2" t="inlineStr">
@@ -33220,7 +33220,11 @@
           <t>PR2ME-PIL-QTY-59-HOP-3420-13-02</t>
         </is>
       </c>
-      <c r="C1054" s="2" t="inlineStr"/>
+      <c r="C1054" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3420-13-02 3422-FC-067 3422-FC-067-M01 2nd Oxide Cleaner Cell 2</t>
+        </is>
+      </c>
       <c r="D1054" s="2" t="inlineStr">
         <is>
           <t>Mechanical</t>
@@ -33228,7 +33232,7 @@
       </c>
       <c r="E1054" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1054" s="2" t="inlineStr">
@@ -33248,7 +33252,11 @@
           <t>PR2ME-PIL-QTY-50-HOP-FT-3420-13-02</t>
         </is>
       </c>
-      <c r="C1055" s="2" t="inlineStr"/>
+      <c r="C1055" s="2" t="inlineStr">
+        <is>
+          <t>Piping HOP of 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
       <c r="D1055" s="2" t="inlineStr">
         <is>
           <t>Piping</t>
@@ -33256,7 +33264,7 @@
       </c>
       <c r="E1055" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1055" s="2" t="inlineStr">
@@ -33276,15 +33284,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-3420-13-02</t>
         </is>
       </c>
-      <c r="C1056" s="2" t="inlineStr"/>
+      <c r="C1056" s="2" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3420-13-02 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
       <c r="D1056" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1056" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1056" s="2" t="inlineStr">
@@ -33304,15 +33316,19 @@
           <t>PR2ME-PIL-QTY-65-HOP-3420-13-02</t>
         </is>
       </c>
-      <c r="C1057" s="2" t="inlineStr"/>
+      <c r="C1057" s="2" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3420-13-02 2nd Oxide Cleaner Cell 2 &amp; Agitator</t>
+        </is>
+      </c>
       <c r="D1057" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="E1057" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1057" s="2" t="inlineStr">
@@ -33332,7 +33348,11 @@
           <t>PR2ME-PIL-QTY-59-HOP-3140-01-01</t>
         </is>
       </c>
-      <c r="C1058" s="2" t="inlineStr"/>
+      <c r="C1058" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3140-01-01 3141-CV-007, 3141-BS-007, 3141-BS-008, 3141-BS-010, 3141-CH-009 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
       <c r="D1058" s="2" t="inlineStr">
         <is>
           <t>Mechanical</t>
@@ -33340,7 +33360,7 @@
       </c>
       <c r="E1058" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1058" s="2" t="inlineStr">
@@ -33360,15 +33380,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-3140-01-01</t>
         </is>
       </c>
-      <c r="C1059" s="2" t="inlineStr"/>
+      <c r="C1059" s="2" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3140-01-01 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1059" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1059" s="2" t="inlineStr">
@@ -33388,15 +33412,19 @@
           <t>PR2ME-PIL-QTY-65-HOP-3140-01-01</t>
         </is>
       </c>
-      <c r="C1060" s="2" t="inlineStr"/>
+      <c r="C1060" s="2" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3140-01-01 SAG Mill Pebble Screen Oversize Conveyor 1</t>
+        </is>
+      </c>
       <c r="D1060" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="E1060" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1060" s="2" t="inlineStr">
@@ -33416,7 +33444,11 @@
           <t>PR2ME-PIL-QTY-59-HOP-3220-07-02</t>
         </is>
       </c>
-      <c r="C1061" s="2" t="inlineStr"/>
+      <c r="C1061" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Subsystem 3220-07-02 3223-SC-404 Ball Mill 6 Crushed Pebble Conveyor Weightometer</t>
+        </is>
+      </c>
       <c r="D1061" s="2" t="inlineStr">
         <is>
           <t>Mechanical</t>
@@ -33424,7 +33456,7 @@
       </c>
       <c r="E1061" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1061" s="2" t="inlineStr">
@@ -33444,15 +33476,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-3220-07-02</t>
         </is>
       </c>
-      <c r="C1062" s="2" t="inlineStr"/>
+      <c r="C1062" s="2" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3220-07-02 Ball Mill 6 Crushed Pebble Conveyor Weightometer</t>
+        </is>
+      </c>
       <c r="D1062" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1062" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1062" s="2" t="inlineStr">
@@ -33472,7 +33508,11 @@
           <t>PR2ME-PIL-QTY-59-HOP-3580-05-01</t>
         </is>
       </c>
-      <c r="C1063" s="2" t="inlineStr"/>
+      <c r="C1063" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Slacking Mill 1 Cyclone Feed Pump 1 &amp; VSD 3580-05-01</t>
+        </is>
+      </c>
       <c r="D1063" s="2" t="inlineStr">
         <is>
           <t>Mechanical</t>
@@ -33480,7 +33520,7 @@
       </c>
       <c r="E1063" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1063" s="2" t="inlineStr">
@@ -33500,7 +33540,11 @@
           <t>PR2ME-PIL-QTY-50-HOP-GWF-3580-05-01</t>
         </is>
       </c>
-      <c r="C1064" s="2" t="inlineStr"/>
+      <c r="C1064" s="2" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Slacking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
       <c r="D1064" s="2" t="inlineStr">
         <is>
           <t>Piping</t>
@@ -33508,7 +33552,7 @@
       </c>
       <c r="E1064" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1064" s="2" t="inlineStr">
@@ -33528,15 +33572,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-3580-05-01</t>
         </is>
       </c>
-      <c r="C1065" s="2" t="inlineStr"/>
+      <c r="C1065" s="2" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-05-01 Lime Slaking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
       <c r="D1065" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1065" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1065" s="2" t="inlineStr">
@@ -33556,15 +33604,19 @@
           <t>PR2ME-PIL-QTY-65-HOP-3580-05-01</t>
         </is>
       </c>
-      <c r="C1066" s="2" t="inlineStr"/>
+      <c r="C1066" s="2" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-05-01 Lime Slaking Mill 1 Cyclone Feed Pump 1 &amp; VSD</t>
+        </is>
+      </c>
       <c r="D1066" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="E1066" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1066" s="2" t="inlineStr">
@@ -33584,7 +33636,11 @@
           <t>PR2ME-PIL-QTY-59-HOP-3580-07-03</t>
         </is>
       </c>
-      <c r="C1067" s="2" t="inlineStr"/>
+      <c r="C1067" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical HOP of Lime Transfer Pumps 3 3580-07-03</t>
+        </is>
+      </c>
       <c r="D1067" s="2" t="inlineStr">
         <is>
           <t>Mechanical</t>
@@ -33592,7 +33648,7 @@
       </c>
       <c r="E1067" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1067" s="2" t="inlineStr">
@@ -33612,7 +33668,11 @@
           <t>PR2ME-PIL-QTY-50-HOP-ML-3580-07-03</t>
         </is>
       </c>
-      <c r="C1068" s="2" t="inlineStr"/>
+      <c r="C1068" s="2" t="inlineStr">
+        <is>
+          <t>Piping HOP of Lime Transfer Pump 3</t>
+        </is>
+      </c>
       <c r="D1068" s="2" t="inlineStr">
         <is>
           <t>Piping</t>
@@ -33620,7 +33680,7 @@
       </c>
       <c r="E1068" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1068" s="2" t="inlineStr">
@@ -33640,15 +33700,19 @@
           <t>PR2ME-PIL-QTY-65-HOP-3580-07-03</t>
         </is>
       </c>
-      <c r="C1069" s="2" t="inlineStr"/>
+      <c r="C1069" s="2" t="inlineStr">
+        <is>
+          <t>Electrical HOP of Subsystem 3580-07-03 Lime Transfer Pump 3</t>
+        </is>
+      </c>
       <c r="D1069" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="E1069" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1069" s="2" t="inlineStr">
@@ -33668,15 +33732,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-3580-07-03</t>
         </is>
       </c>
-      <c r="C1070" s="2" t="inlineStr"/>
+      <c r="C1070" s="2" t="inlineStr">
+        <is>
+          <t>Instrument HOP of Subsystem 3580-07-03 Lime Transfer Pump 3</t>
+        </is>
+      </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1070" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1070" s="2" t="inlineStr">
@@ -33696,15 +33764,19 @@
           <t>PR2ME-PIL-QTY-70-HOP-2191-90-01</t>
         </is>
       </c>
-      <c r="C1071" s="2" t="inlineStr"/>
+      <c r="C1071" s="2" t="inlineStr">
+        <is>
+          <t>Instrument (PCS) HOP of Subsystem 2191-90-01 Camera-Network</t>
+        </is>
+      </c>
       <c r="D1071" s="2" t="inlineStr">
         <is>
-          <t>No Discipline</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E1071" s="2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPLOADED_FILE</t>
         </is>
       </c>
       <c r="F1071" s="2" t="inlineStr">
